--- a/excel/distribuidora-aurelio-s-a-c_capacitaciones.xlsx
+++ b/excel/distribuidora-aurelio-s-a-c_capacitaciones.xlsx
@@ -598,12 +598,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C001114205</t>
+          <t>C000957650</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C001114205 - AURIS QUISPE SILVIA NANCY</t>
+          <t>C000957650 - SULLCAPUMA OBAQUE DE CUEVA URSULA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -634,7 +634,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -688,12 +688,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C001174840</t>
+          <t>C000961032</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C001174840 - FUENTES BERMEO ROSANA ALINDA</t>
+          <t>C000961032 - BENAVIDES MAGALLANES DE LAURENTE MARIA S</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -724,7 +724,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C001376539</t>
+          <t>C001114205</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C001376539 - CARPIO JUNES JOSEFINA</t>
+          <t>C001114205 - AURIS QUISPE SILVIA NANCY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -814,7 +814,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
@@ -868,12 +868,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C000957650</t>
+          <t>C001379004</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C000957650 - SULLCAPUMA OBAQUE DE CUEVA URSULA</t>
+          <t>C001379004 - MUNANTE DE GONZALES CARMELA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C000961032</t>
+          <t>C001376539</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C000961032 - BENAVIDES MAGALLANES DE LAURENTE MARIA S</t>
+          <t>C001376539 - CARPIO JUNES JOSEFINA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001379004</t>
+          <t>C001174840</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C001379004 - MUNANTE DE GONZALES CARMELA</t>
+          <t>C001174840 - FUENTES BERMEO ROSANA ALINDA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1174,12 +1174,12 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001450198</t>
+          <t>C001644118</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C001450198 - SALVADOR ALMEYDA MARITZA MAXIMILIANA</t>
+          <t>C001644118 - MARCOS PILPE SHIRLE EDITH</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,12 +1264,12 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C001487012</t>
+          <t>C001531013</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C001487012 - CHACALIAZA CHACALTANA MARIA DEL CARMEN</t>
+          <t>C001531013 - TORRES ORTIZ GIOVANNA DEL PILAR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C001495761</t>
+          <t>C001450198</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C001495761 - GARCIA TELLO VICTORIA</t>
+          <t>C001450198 - SALVADOR ALMEYDA MARITZA MAXIMILIANA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001531013</t>
+          <t>C001487012</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C001531013 - TORRES ORTIZ GIOVANNA DEL PILAR</t>
+          <t>C001487012 - CHACALIAZA CHACALTANA MARIA DEL CARMEN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001644118</t>
+          <t>C001495761</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C001644118 - MARCOS PILPE SHIRLE EDITH</t>
+          <t>C001495761 - GARCIA TELLO VICTORIA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1624,12 +1624,12 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C004009166</t>
+          <t>C004243890</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C004009166 - TORRES HILARIO JOEL MARTIN</t>
+          <t>C004243890 - PECHO ALMEYDA SANTA ROSA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C004177967</t>
+          <t>C004212960</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C004177967 - TORRES RAMOS MIRTHA JUDITH</t>
+          <t>C004212960 - CHANCA DE LA MATA SABINA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1893,16 +1893,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1918,13 +1914,17 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C004178891</t>
+          <t>C004177967</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C004178891 - MOLINA FUENTES DE MORE ELIZABETH</t>
+          <t>C004177967 - TORRES RAMOS MIRTHA JUDITH</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1987,12 +1987,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2008,17 +2012,13 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2050,12 +2050,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C004014363</t>
+          <t>C004178891</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C004014363 - SANCHEZ VALENZUELA LUZ URIETA</t>
+          <t>C004178891 - MOLINA FUENTES DE MORE ELIZABETH</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2086,7 +2086,7 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2102,13 +2102,17 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2144,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C004212960</t>
+          <t>C004014363</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C004212960 - CHANCA DE LA MATA SABINA</t>
+          <t>C004014363 - SANCHEZ VALENZUELA LUZ URIETA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2176,7 +2180,7 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2192,17 +2196,13 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C004243890</t>
+          <t>C004009166</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C004243890 - PECHO ALMEYDA SANTA ROSA</t>
+          <t>C004009166 - TORRES HILARIO JOEL MARTIN</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001391394</t>
+          <t>C001493339</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C001391394 - FARFAN CHIRA MARILU GIOVANA</t>
+          <t>C001493339 - SALVADOR MENESES ROSA HILDA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2360,33 +2360,29 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2418,12 +2414,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C001513764</t>
+          <t>C001504560</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>C001513764 - TASAYCO PACHAS CARLOS ALBERTO</t>
+          <t>C001504560 - MAGALLANES MATEO MARIA ANGELICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2508,12 +2504,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C001530326</t>
+          <t>C001506187</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C001530326 - MARCELO GONZALES MIRTHA</t>
+          <t>C001506187 - CAYCHO FLORES DE GUTIERREZ LUCILA DORA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2544,12 +2540,12 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2560,13 +2556,17 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C001504560</t>
+          <t>C001513764</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C001504560 - MAGALLANES MATEO MARIA ANGELICA</t>
+          <t>C001513764 - TASAYCO PACHAS CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C001506187</t>
+          <t>C001530326</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C001506187 - CAYCHO FLORES DE GUTIERREZ LUCILA DORA</t>
+          <t>C001530326 - MARCELO GONZALES MIRTHA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2814,12 +2814,12 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2830,17 +2830,13 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2872,12 +2868,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C001493339</t>
+          <t>C000960971</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C001493339 - SALVADOR MENESES ROSA HILDA</t>
+          <t>C000960971 - TICONA URRUCHI SOCORRO MERCEDES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2908,17 +2904,17 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -2962,12 +2958,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001414285</t>
+          <t>C001215499</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C001414285 - GUILLEN MENDIZ CRISTINA BLANCA</t>
+          <t>C001215499 - APOLAYA GONZALES ANGELICA MILAGROS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2998,12 +2994,12 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3052,12 +3048,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C001740943</t>
+          <t>C001391394</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C001740943 - ROJAS AVALOS JOSE ORLANDO</t>
+          <t>C001391394 - FARFAN CHIRA MARILU GIOVANA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3093,7 +3089,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3104,13 +3100,17 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3142,12 +3142,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C004014318</t>
+          <t>C001414285</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C004014318 - URIONDO YATACO GLADYS AMALIA</t>
+          <t>C001414285 - GUILLEN MENDIZ CRISTINA BLANCA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3178,12 +3178,12 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C004161274</t>
+          <t>C001740943</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C004161274 - GUERRA MARTINEZ SILVESTRE PAULINO</t>
+          <t>C001740943 - ROJAS AVALOS JOSE ORLANDO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3322,12 +3322,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C004101162</t>
+          <t>C004014318</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C004101162 - CRISTOBAL PALOMINO SONIA</t>
+          <t>C004014318 - URIONDO YATACO GLADYS AMALIA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3358,7 +3358,7 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C004174277</t>
+          <t>C004101162</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C004174277 - ORELLANA ATUNCAR EDUARDO JESUS</t>
+          <t>C004101162 - CRISTOBAL PALOMINO SONIA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3538,12 +3538,12 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C001215499</t>
+          <t>C004161274</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C001215499 - APOLAYA GONZALES ANGELICA MILAGROS</t>
+          <t>C004161274 - GUERRA MARTINEZ SILVESTRE PAULINO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3628,7 +3628,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C000960971</t>
+          <t>C004174277</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C000960971 - TICONA URRUCHI SOCORRO MERCEDES</t>
+          <t>C004174277 - ORELLANA ATUNCAR EDUARDO JESUS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3718,7 +3718,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001516754</t>
+          <t>C001404952</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C001516754 - DE LA MATTA TORNERO NOEMI OLIVA</t>
+          <t>C001404952 - MATOS MELGAR YUNY BERCY</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C004172844</t>
+          <t>C001493102</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C004172844 - PASTRANA DEL SUR S.A.C.</t>
+          <t>C001493102 - CANCHERO CURACA JULIA ALEJANDRINA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3896,21 +3896,9 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Mejor experiencia con la app</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
@@ -3952,12 +3940,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C004028243</t>
+          <t>C001522838</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C004028243 - ROJAS CUSIPUMA HERLINDA YESENIA</t>
+          <t>C001522838 - NAPANGA DELGADO ORLANDO JEANPIER</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3988,7 +3976,7 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3998,7 +3986,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -4042,12 +4030,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C004001775</t>
+          <t>C000957354</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C004001775 - CUSIPUMA LAZA YANDEL VALERIO</t>
+          <t>C000957354 - DE LA CRUZ BOHORQUEZ ROSA VIRGINIA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4078,12 +4066,12 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4132,12 +4120,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C004059687</t>
+          <t>C000961480</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C004059687 - VILCAPUMA MARQUEZ DE DAVALOS PAOLA</t>
+          <t>C000961480 - COLQUEPISCO FLORES JUANA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4173,7 +4161,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4222,12 +4210,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C004210126</t>
+          <t>C001516754</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C004210126 - ALVAREZ TINEO MARLENI</t>
+          <t>C001516754 - DE LA MATTA TORNERO NOEMI OLIVA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4258,7 +4246,7 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -4268,7 +4256,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -4312,12 +4300,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C000957354</t>
+          <t>C004001775</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C000957354 - DE LA CRUZ BOHORQUEZ ROSA VIRGINIA</t>
+          <t>C004001775 - CUSIPUMA LAZA YANDEL VALERIO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4348,12 +4336,12 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4402,12 +4390,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001716816</t>
+          <t>C001742520</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001716816 - MARTINEZ CANDIOTTE JOHAN JOHNSON</t>
+          <t>C001742520 - REYES RAMOS DIANA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4438,7 +4426,7 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -4492,12 +4480,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C004008260</t>
+          <t>C001716813</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C004008260 - VALERIANO CHALLCO AURELIA</t>
+          <t>C001716813 - LINO GARCIA DARLINE FERNANDA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4533,12 +4521,12 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
@@ -4582,12 +4570,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C004014359</t>
+          <t>C004210126</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C004014359 - CANTO HUARACA CECILIA ROSANA</t>
+          <t>C004210126 - ALVAREZ TINEO MARLENI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4618,7 +4606,7 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4628,7 +4616,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
@@ -4672,12 +4660,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C000961480</t>
+          <t>C004172844</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C000961480 - COLQUEPISCO FLORES JUANA</t>
+          <t>C004172844 - PASTRANA DEL SUR S.A.C.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4713,12 +4701,12 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
@@ -4762,12 +4750,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001404952</t>
+          <t>C004059687</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C001404952 - MATOS MELGAR YUNY BERCY</t>
+          <t>C004059687 - VILCAPUMA MARQUEZ DE DAVALOS PAOLA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4798,12 +4786,12 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4842,7 +4830,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4852,17 +4840,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C001493102</t>
+          <t>C004008260</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C001493102 - CANCHERO CURACA JULIA ALEJANDRINA</t>
+          <t>C004008260 - VALERIANO CHALLCO AURELIA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
@@ -4875,7 +4863,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4886,9 +4874,21 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Poco dispuesto</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
@@ -4930,12 +4930,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C001522838</t>
+          <t>C004014359</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C001522838 - NAPANGA DELGADO ORLANDO JEANPIER</t>
+          <t>C004014359 - CANTO HUARACA CECILIA ROSANA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4966,7 +4966,7 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S50" t="inlineStr"/>
@@ -5020,12 +5020,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C004036901</t>
+          <t>C004016313</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C004036901 - CANCHERO CURACA BERTHA ALEJANDRINA</t>
+          <t>C004016313 - PALOMINO AGUADO CELINDA YSABEL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5056,12 +5056,12 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001704992</t>
+          <t>C004028243</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C001704992 - VASQUEZ CHUQUISPUMA EVELYN</t>
+          <t>C004028243 - ROJAS CUSIPUMA HERLINDA YESENIA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5146,12 +5146,12 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001716813</t>
+          <t>C004036901</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C001716813 - LINO GARCIA DARLINE FERNANDA</t>
+          <t>C004036901 - CANCHERO CURACA BERTHA ALEJANDRINA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5236,7 +5236,7 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C004016313</t>
+          <t>C001716816</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C004016313 - PALOMINO AGUADO CELINDA YSABEL</t>
+          <t>C001716816 - MARTINEZ CANDIOTTE JOHAN JOHNSON</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001742520</t>
+          <t>C001704992</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C001742520 - REYES RAMOS DIANA</t>
+          <t>C001704992 - VASQUEZ CHUQUISPUMA EVELYN</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C001748704</t>
+          <t>C001511764</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C001748704 - ASTORAYME DE QUISPE MARIA DEL CARMEN</t>
+          <t>C001511764 - ASTORAYME BENDEZU CINTHIA YESSENIA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C001732725</t>
+          <t>C001495385</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C001732725 - LANDEO FLORES YORFA</t>
+          <t>C001495385 - AYASTA FELIX NORMA ZOILA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5650,12 +5650,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C004240083</t>
+          <t>C001405847</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C004240083 - SANCA FLOREZ JUDITH</t>
+          <t>C001405847 - DIAZ VELASQUEZ DE SESSAREGO MARIA PIEDAD</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5686,12 +5686,12 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C004210148</t>
+          <t>C001489307</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C004210148 - PEREZ DE SANCHEZ JONNY HILDA</t>
+          <t>C001489307 - SOLORZANO MITMA RICHAR</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C001530822</t>
+          <t>C001629771</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C001530822 - REYES QUISPE SANTA ANGELICA</t>
+          <t>C001629771 - ROJAS RODRIGUEZ MARIA ESTHER</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5866,7 +5866,7 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C001511764</t>
+          <t>C004013408</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C001511764 - ASTORAYME BENDEZU CINTHIA YESSENIA</t>
+          <t>C004013408 - QUISPE QUISPE ELIZABETH WENDY</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C001504541</t>
+          <t>C001732725</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C001504541 - CARBAJAL ORTIZ MARIA LILIA</t>
+          <t>C001732725 - LANDEO FLORES YORFA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6046,12 +6046,12 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C001495385</t>
+          <t>C004240083</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C001495385 - AYASTA FELIX NORMA ZOILA</t>
+          <t>C004240083 - SANCA FLOREZ JUDITH</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C001405847</t>
+          <t>C004210148</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C001405847 - DIAZ VELASQUEZ DE SESSAREGO MARIA PIEDAD</t>
+          <t>C004210148 - PEREZ DE SANCHEZ JONNY HILDA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6226,7 +6226,7 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001489307</t>
+          <t>C004176093</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C001489307 - SOLORZANO MITMA RICHAR</t>
+          <t>C004176093 - ZAMBRANO CASTILLA GYLARY LAILA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6316,7 +6316,7 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S65" t="inlineStr"/>
@@ -6370,12 +6370,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C001629771</t>
+          <t>C004061401</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C001629771 - ROJAS RODRIGUEZ MARIA ESTHER</t>
+          <t>C004061401 - FIGUEROA CASTILLA WILLIAM JAVIER</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C004007837</t>
+          <t>C004095681</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C004007837 - QUISPE CRUZ SONIA</t>
+          <t>C004095681 - PACHAS PACHAS MARIA YSABEL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6496,7 +6496,7 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C004095681</t>
+          <t>C004007837</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C004095681 - PACHAS PACHAS MARIA YSABEL</t>
+          <t>C004007837 - QUISPE CRUZ SONIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6586,7 +6586,7 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C004061401</t>
+          <t>C001165037</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>C004061401 - FIGUEROA CASTILLA WILLIAM JAVIER</t>
+          <t>C001165037 - QUIROZ VERA ROSA ELIZABETH</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6671,7 +6671,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -6730,12 +6734,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C004176093</t>
+          <t>C001738163</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C004176093 - ZAMBRANO CASTILLA GYLARY LAILA</t>
+          <t>C001738163 - GUTIERREZ ROJAS CLEMENTINA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6766,17 +6770,17 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S70" t="inlineStr"/>
@@ -6820,12 +6824,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C001541280</t>
+          <t>C001748704</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C001541280 - VIVANCO GARCIA MARIBEL</t>
+          <t>C001748704 - ASTORAYME DE QUISPE MARIA DEL CARMEN</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6910,12 +6914,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C001653241</t>
+          <t>C001541280</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C001653241 - BOLO MINAYA JUANA JULIA</t>
+          <t>C001541280 - VIVANCO GARCIA MARIBEL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6951,7 +6955,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7000,12 +7004,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001738163</t>
+          <t>C001653241</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C001738163 - GUTIERREZ ROJAS CLEMENTINA</t>
+          <t>C001653241 - BOLO MINAYA JUANA JULIA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7036,12 +7040,12 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -7090,12 +7094,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C004013408</t>
+          <t>C001504541</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C004013408 - QUISPE QUISPE ELIZABETH WENDY</t>
+          <t>C001504541 - CARBAJAL ORTIZ MARIA LILIA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7126,12 +7130,12 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7180,12 +7184,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C001168647</t>
+          <t>C001530822</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C001168647 - MEZA BENDEZU ROCIO RENE</t>
+          <t>C001530822 - REYES QUISPE SANTA ANGELICA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7216,7 +7220,7 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -7270,12 +7274,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001165037</t>
+          <t>C001168647</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C001165037 - QUIROZ VERA ROSA ELIZABETH</t>
+          <t>C001168647 - MEZA BENDEZU ROCIO RENE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7301,11 +7305,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>C001086594</t>
+          <t>C000957808</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>C001086594 - RAMOS CAHUANA SONIA ISABEL</t>
+          <t>C000957808 - NAPANGA PEREZ BALBINA ISIDORA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>C000957808</t>
+          <t>C000960458</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>C000957808 - NAPANGA PEREZ BALBINA ISIDORA</t>
+          <t>C000960458 - VERA NUNEZ NORMA GREGORIA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10292,7 +10292,7 @@
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -10308,17 +10308,13 @@
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10350,12 +10346,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>C000960458</t>
+          <t>C001086594</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>C000960458 - VERA NUNEZ NORMA GREGORIA</t>
+          <t>C001086594 - RAMOS CAHUANA SONIA ISABEL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10386,7 +10382,7 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -10402,13 +10398,17 @@
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10440,12 +10440,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C004065232</t>
+          <t>C001159487</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>C004065232 - AGUADO LOPEZ CHAI TIODOLINDA</t>
+          <t>C001159487 - ESPINO LOZA OLIVIA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10476,7 +10476,7 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -10486,23 +10486,19 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10992,12 +10988,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C001733927</t>
+          <t>C004065232</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C001733927 - RODRIGUEZ PALOMINO LESLY JULISSA</t>
+          <t>C004065232 - AGUADO LOPEZ CHAI TIODOLINDA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -11033,24 +11029,28 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11082,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C001733929</t>
+          <t>C001733927</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>C001733929 - SALVATIERRA MOTTA YAMELI MILAGROS</t>
+          <t>C001733927 - RODRIGUEZ PALOMINO LESLY JULISSA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11118,7 +11118,7 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S118" t="inlineStr"/>
@@ -11172,12 +11172,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>C001511045</t>
+          <t>C001733929</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>C001511045 - AROTINCO DE DURAND SANTA BARBARA</t>
+          <t>C001733929 - SALVATIERRA MOTTA YAMELI MILAGROS</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S119" t="inlineStr"/>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Tuvo una mala experiencia previa usando Diadía</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -11262,17 +11262,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>C001433290</t>
+          <t>C001511045</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>C001433290 - BELLEZA CARPIO ANGELA ELIZABETH</t>
+          <t>C001511045 - AROTINCO DE DURAND SANTA BARBARA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -11296,9 +11296,21 @@
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Poco dispuesto</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr">
         <is>
@@ -11330,7 +11342,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tuvo una mala experiencia previa usando Diadía</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -11340,17 +11352,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>C001159487</t>
+          <t>C001433290</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>C001159487 - ESPINO LOZA OLIVIA</t>
+          <t>C001433290 - BELLEZA CARPIO ANGELA ELIZABETH</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
@@ -11363,7 +11375,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -11374,21 +11386,9 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Poco dispuesto</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr">
         <is>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>C004013473</t>
+          <t>C004029945</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>C004013473 - TASAYCO SARAVIA WALTER</t>
+          <t>C004029945 - BAUTISTA CHOQUE JUAN MARTIN</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S123" t="inlineStr"/>
@@ -11614,12 +11614,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C004029945</t>
+          <t>C004061404</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>C004029945 - BAUTISTA CHOQUE JUAN MARTIN</t>
+          <t>C004061404 - MENDOZA HERRERA ROCIO ELIZABETH</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11645,12 +11645,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -11704,12 +11708,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C004061404</t>
+          <t>C001532127</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>C004061404 - MENDOZA HERRERA ROCIO ELIZABETH</t>
+          <t>C001532127 - TASAYCO SITU ENZO GIUSEPPE</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11735,16 +11739,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C001532127</t>
+          <t>C001556308</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>C001532127 - TASAYCO SITU ENZO GIUSEPPE</t>
+          <t>C001556308 - HUISA HUARACA MERCEDES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11850,13 +11850,17 @@
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11888,12 +11892,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C001556308</t>
+          <t>C001493327</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>C001556308 - HUISA HUARACA MERCEDES</t>
+          <t>C001493327 - OLIVERO TORRES GLORIA YSABEL</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11924,12 +11928,12 @@
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -11940,17 +11944,13 @@
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11982,12 +11982,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C001493327</t>
+          <t>C004013473</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>C001493327 - OLIVERO TORRES GLORIA YSABEL</t>
+          <t>C004013473 - TASAYCO SARAVIA WALTER</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -12018,7 +12018,7 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S128" t="inlineStr"/>
@@ -12882,12 +12882,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>C000960466</t>
+          <t>C001288661</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>C000960466 - LAURA CANCHARI OSWALDO ROQUE</t>
+          <t>C001288661 - SIGUAS CAMPOS DE ROMERO CANDELARIA VICTO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S138" t="inlineStr"/>
@@ -12972,12 +12972,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>C000962609</t>
+          <t>C001172358</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>C000962609 - RODRIGUEZ GUILLEN DAYSI</t>
+          <t>C001172358 - AURIS PAUCAR FELIPA FLORINDA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -13024,17 +13024,13 @@
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -13066,12 +13062,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>C001172358</t>
+          <t>C000960466</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>C001172358 - AURIS PAUCAR FELIPA FLORINDA</t>
+          <t>C000960466 - LAURA CANCHARI OSWALDO ROQUE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -13107,7 +13103,7 @@
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -13156,12 +13152,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>C001541087</t>
+          <t>C000962609</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>C001541087 - VENTO INGA MARIA ISABEL</t>
+          <t>C000962609 - RODRIGUEZ GUILLEN DAYSI</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -13208,13 +13204,17 @@
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>C001379080</t>
+          <t>C001541087</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>C001379080 - MORAN DE GONZALES ROSA MARIA</t>
+          <t>C001541087 - VENTO INGA MARIA ISABEL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -13282,7 +13282,7 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -13292,23 +13292,19 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -13340,12 +13336,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>C001319591</t>
+          <t>C001508435</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>C001319591 - LEVANO CHUQUISPUMA FABIANA SIMONA</t>
+          <t>C001508435 - AGUIRRE SANTIAGO GABRIELA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -13376,17 +13372,17 @@
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S143" t="inlineStr"/>
@@ -13430,12 +13426,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>C001288661</t>
+          <t>C001481441</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>C001288661 - SIGUAS CAMPOS DE ROMERO CANDELARIA VICTO</t>
+          <t>C001481441 - RAMOS DE ROJAS YRMA ESTHER</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -13466,17 +13462,17 @@
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S144" t="inlineStr"/>
@@ -13520,12 +13516,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>C001508435</t>
+          <t>C001489129</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>C001508435 - AGUIRRE SANTIAGO GABRIELA</t>
+          <t>C001489129 - RODRIGUEZ GUILLEN ANA ZORAIDA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -13610,12 +13606,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>C001427276</t>
+          <t>C001490615</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>C001427276 - SALAZAR ROJAS FLOR DE MARIA</t>
+          <t>C001490615 - VARA PANCA EVELYN SUSANA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -13646,12 +13642,12 @@
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -13700,12 +13696,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>C001430224</t>
+          <t>C001427276</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>C001430224 - LEVANO RAMOS MAGALLY ROCIO</t>
+          <t>C001427276 - SALAZAR ROJAS FLOR DE MARIA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -13741,12 +13737,12 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S147" t="inlineStr"/>
@@ -13790,12 +13786,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>C001481441</t>
+          <t>C001430224</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>C001481441 - RAMOS DE ROJAS YRMA ESTHER</t>
+          <t>C001430224 - LEVANO RAMOS MAGALLY ROCIO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -13836,7 +13832,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S148" t="inlineStr"/>
@@ -13880,12 +13876,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>C001489129</t>
+          <t>C001319591</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>C001489129 - RODRIGUEZ GUILLEN ANA ZORAIDA</t>
+          <t>C001319591 - LEVANO CHUQUISPUMA FABIANA SIMONA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -13916,17 +13912,17 @@
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S149" t="inlineStr"/>
@@ -13970,12 +13966,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>C001490615</t>
+          <t>C001379080</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>C001490615 - VARA PANCA EVELYN SUSANA</t>
+          <t>C001379080 - MORAN DE GONZALES ROSA MARIA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -14006,29 +14002,33 @@
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -14060,12 +14060,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>C004188826</t>
+          <t>C004178433</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>C004188826 - VELASQUEZ DIANDERAS CELIA SOBEIDA</t>
+          <t>C004178433 - PARI DE LAURA ROSA EUFRACIA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S151" t="inlineStr"/>
@@ -14150,12 +14150,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>C004178433</t>
+          <t>C004188826</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>C004178433 - PARI DE LAURA ROSA EUFRACIA</t>
+          <t>C004188826 - VELASQUEZ DIANDERAS CELIA SOBEIDA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S152" t="inlineStr"/>
@@ -14240,12 +14240,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>C004049669</t>
+          <t>C004032632</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>C004049669 - HERRERA AGUIRRE CINDY</t>
+          <t>C004032632 - MAGALLANES QUIROZ DE TASAYCO CARMEN LUIS</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -14281,28 +14281,24 @@
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S153" t="inlineStr"/>
       <c r="T153" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -14334,12 +14330,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C004032632</t>
+          <t>C004049669</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>C004032632 - MAGALLANES QUIROZ DE TASAYCO CARMEN LUIS</t>
+          <t>C004049669 - HERRERA AGUIRRE CINDY</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14375,24 +14371,28 @@
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U154" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15160,12 +15160,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>C001541713</t>
+          <t>C001307050</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>C001541713 - CANALES AYLLON RUTH LADY</t>
+          <t>C001307050 - QUISPE NORMA BERNARDINA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -15196,12 +15196,12 @@
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -15212,13 +15212,17 @@
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15434,12 +15438,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>C001497344</t>
+          <t>C001541713</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>C001497344 - EMPRESA COMERCIAL DISTRIBUIDORA H &amp; C S.</t>
+          <t>C001541713 - CANALES AYLLON RUTH LADY</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -15470,7 +15474,7 @@
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -15480,7 +15484,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S166" t="inlineStr"/>
@@ -15524,12 +15528,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>C001307050</t>
+          <t>C001497344</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>C001307050 - QUISPE NORMA BERNARDINA</t>
+          <t>C001497344 - EMPRESA COMERCIAL DISTRIBUIDORA H &amp; C S.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -15560,33 +15564,29 @@
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -15712,12 +15712,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>C004028744</t>
+          <t>C004049158</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>C004028744 - ABURTO YATACO ALEX ROBERTO</t>
+          <t>C004049158 - HILARION HUAYLLA JOSE LUIS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -15748,12 +15748,12 @@
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -15764,17 +15764,13 @@
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -15806,12 +15802,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>C004049158</t>
+          <t>C004028744</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>C004049158 - HILARION HUAYLLA JOSE LUIS</t>
+          <t>C004028744 - ABURTO YATACO ALEX ROBERTO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -15842,12 +15838,12 @@
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -15858,13 +15854,17 @@
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -16542,12 +16542,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>C004169879</t>
+          <t>C004094381</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>C004169879 - CHAVEZ CAHUANA LILI ZUNILDA</t>
+          <t>C004094381 - TORRES RIVAS DAYANA KAREN</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -16578,17 +16578,17 @@
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="S178" t="inlineStr"/>
@@ -16730,12 +16730,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>C004060561</t>
+          <t>C004169879</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>C004060561 - VELASQUEZ MONTEROLA JESUS ETEL</t>
+          <t>C004169879 - CHAVEZ CAHUANA LILI ZUNILDA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -16766,12 +16766,12 @@
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -16782,13 +16782,17 @@
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U180" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -16820,12 +16824,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>C004094381</t>
+          <t>C004060561</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>C004094381 - TORRES RIVAS DAYANA KAREN</t>
+          <t>C004060561 - VELASQUEZ MONTEROLA JESUS ETEL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -16866,23 +16870,19 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -16914,12 +16914,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>C004029962</t>
+          <t>C004011479</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>C004029962 - OJEDA OJEDA JULIANA ROSARIO</t>
+          <t>C004011479 - MAGUINA LOPEZ SHIRLEY DESSIREDT</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -16971,12 +16971,12 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17008,12 +17008,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>C004038222</t>
+          <t>C004029962</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>C004038222 - VILCAPUMA LAURA RUBY EDELYN</t>
+          <t>C004029962 - OJEDA OJEDA JULIANA ROSARIO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -17065,12 +17065,12 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -17102,12 +17102,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>C004038716</t>
+          <t>C004038222</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>C004038716 - JUSCAMAITA FLORES MILENNE MIRIAM</t>
+          <t>C004038222 - VILCAPUMA LAURA RUBY EDELYN</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -17138,7 +17138,7 @@
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -17154,13 +17154,17 @@
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U184" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17192,12 +17196,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>C001728535</t>
+          <t>C004038716</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>C001728535 - AURIS CHAVEZ DE CASTILLON ALICIA MARTINA</t>
+          <t>C004038716 - JUSCAMAITA FLORES MILENNE MIRIAM</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -17244,17 +17248,13 @@
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -17380,12 +17380,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>C004011479</t>
+          <t>C001721221</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>C004011479 - MAGUINA LOPEZ SHIRLEY DESSIREDT</t>
+          <t>C001721221 - IDONE YACTAYO ZAIRA VERONICA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -17416,7 +17416,7 @@
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
@@ -17432,17 +17432,13 @@
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -17474,12 +17470,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>C001721221</t>
+          <t>C001728535</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>C001721221 - IDONE YACTAYO ZAIRA VERONICA</t>
+          <t>C001728535 - AURIS CHAVEZ DE CASTILLON ALICIA MARTINA</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -17526,13 +17522,17 @@
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U188" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17658,12 +17658,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>C001551841</t>
+          <t>C001522451</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>C001551841 - TASAYCO MAGALLANES YEISY MEDALIT</t>
+          <t>C001522451 - CARCAMO DE ROJAS DACIANA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -17694,7 +17694,7 @@
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
@@ -17752,12 +17752,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>C001498029</t>
+          <t>C001517282</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>C001498029 - CASTILLON HERRERA KLEYBER YONZON</t>
+          <t>C001517282 - CLAROS FELIX JESSICA DEL ROSARIO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -17793,7 +17793,7 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -17846,12 +17846,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>C001517282</t>
+          <t>C001551841</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>C001517282 - CLAROS FELIX JESSICA DEL ROSARIO</t>
+          <t>C001551841 - TASAYCO MAGALLANES YEISY MEDALIT</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -17882,12 +17882,12 @@
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>C001522451</t>
+          <t>C001365658</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>C001522451 - CARCAMO DE ROJAS DACIANA</t>
+          <t>C001365658 - PAUCAR CRISOSTOMO ZENAIDA SEREGIA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -17976,7 +17976,7 @@
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -18034,12 +18034,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>C001365658</t>
+          <t>C001498029</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>C001365658 - PAUCAR CRISOSTOMO ZENAIDA SEREGIA</t>
+          <t>C001498029 - CASTILLON HERRERA KLEYBER YONZON</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -18070,7 +18070,7 @@
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -18786,12 +18786,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>C001477089</t>
+          <t>C001490980</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>C001477089 - VIDALON NOA DELIA BERTHA</t>
+          <t>C001490980 - ROJAS ATUNCAR VICTOR JAVIER</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -18817,7 +18817,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
@@ -18827,7 +18831,7 @@
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -18843,12 +18847,12 @@
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18880,12 +18884,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>C001490980</t>
+          <t>C001477089</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>C001490980 - ROJAS ATUNCAR VICTOR JAVIER</t>
+          <t>C001477089 - VIDALON NOA DELIA BERTHA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -18911,11 +18915,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -18941,12 +18941,12 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V203" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>C004179159</t>
+          <t>C004058896</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>C004179159 - SILVA VILCHERREZ CARITO ELIZABETH</t>
+          <t>C004058896 - CARPIO PACHAS LUISA NELLY</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -19198,33 +19198,29 @@
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -19256,12 +19252,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>C004058896</t>
+          <t>C004030081</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>C004058896 - CARPIO PACHAS LUISA NELLY</t>
+          <t>C004030081 - ATUNCAR ATUNCAR MARIA STEPHANY</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -19292,12 +19288,12 @@
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
@@ -19346,12 +19342,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>C004030081</t>
+          <t>C004030082</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>C004030081 - ATUNCAR ATUNCAR MARIA STEPHANY</t>
+          <t>C004030082 - YATACO MUNAYCO YSABEL</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -19382,7 +19378,7 @@
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
@@ -19398,13 +19394,17 @@
       <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U208" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -19436,12 +19436,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>C004030082</t>
+          <t>C004030084</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>C004030082 - YATACO MUNAYCO YSABEL</t>
+          <t>C004030084 - ATUNCAR FUENTES ELIZABETH PAOLA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -19472,7 +19472,7 @@
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S209" t="inlineStr"/>
@@ -19530,12 +19530,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>C004030084</t>
+          <t>C004039877</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>C004030084 - ATUNCAR FUENTES ELIZABETH PAOLA</t>
+          <t>C004039877 - NAVARRO MARCELO ANITA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -19566,17 +19566,17 @@
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S210" t="inlineStr"/>
@@ -19624,12 +19624,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C004039877</t>
+          <t>C004039883</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>C004039877 - NAVARRO MARCELO ANITA</t>
+          <t>C004039883 - OCHOA PACHAS DE MENDOZA SOLEDAD</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -19660,7 +19660,7 @@
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -19718,12 +19718,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C004039883</t>
+          <t>C004040873</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>C004039883 - OCHOA PACHAS DE MENDOZA SOLEDAD</t>
+          <t>C004040873 - ALVARADO TASSARA SANDRA NATALIA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -19754,7 +19754,7 @@
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -19770,17 +19770,13 @@
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -19812,12 +19808,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>C004040873</t>
+          <t>C004044079</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>C004040873 - ALVARADO TASSARA SANDRA NATALIA</t>
+          <t>C004044079 - VALLADARES ESPINOZA GLADYS MARILU</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -19864,13 +19860,17 @@
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U213" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -19902,12 +19902,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>C004044079</t>
+          <t>C004069734</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>C004044079 - VALLADARES ESPINOZA GLADYS MARILU</t>
+          <t>C004069734 - AMBROSIO MELO MONICA LISSET</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -19938,33 +19938,29 @@
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="S214" t="inlineStr"/>
       <c r="T214" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -19996,12 +19992,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>C004069734</t>
+          <t>C004179159</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>C004069734 - AMBROSIO MELO MONICA LISSET</t>
+          <t>C004179159 - SILVA VILCHERREZ CARITO ELIZABETH</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -20032,7 +20028,7 @@
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -20042,19 +20038,23 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S215" t="inlineStr"/>
       <c r="T215" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U215" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -20458,12 +20458,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>C001655766</t>
+          <t>C001653300</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>C001655766 - PACHAS NAVARRO JESUS MARTIN</t>
+          <t>C001653300 - CCAPA CRUZ JUANA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -20489,11 +20489,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
@@ -20503,7 +20499,7 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -20556,12 +20552,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C001653300</t>
+          <t>C001655766</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>C001653300 - CCAPA CRUZ JUANA</t>
+          <t>C001655766 - PACHAS NAVARRO JESUS MARTIN</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -20587,7 +20583,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -21402,12 +21402,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>C001526666</t>
+          <t>C001319626</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>C001526666 - CANALES AYLLON YESSICA KELLY</t>
+          <t>C001319626 - TUPAC VILCAPUMA MARITZA EDITH</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -21496,12 +21496,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>C001505052</t>
+          <t>C001646860</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>C001505052 - VELASQUEZ ALCA FIORELLA YESICA</t>
+          <t>C001646860 - MARTINEZ VALENCIA JULLIANA DEL CARMEN</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -21532,7 +21532,7 @@
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -21542,7 +21542,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S231" t="inlineStr"/>
@@ -21553,12 +21553,12 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21590,12 +21590,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>C001646860</t>
+          <t>C001526666</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>C001646860 - MARTINEZ VALENCIA JULLIANA DEL CARMEN</t>
+          <t>C001526666 - CANALES AYLLON YESSICA KELLY</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -21626,12 +21626,12 @@
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
@@ -21684,12 +21684,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>C001319626</t>
+          <t>C001505052</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>C001319626 - TUPAC VILCAPUMA MARITZA EDITH</t>
+          <t>C001505052 - VELASQUEZ ALCA FIORELLA YESICA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -21720,17 +21720,17 @@
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S233" t="inlineStr"/>
@@ -21741,12 +21741,12 @@
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -21872,12 +21872,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>C004178891</t>
+          <t>C004187618</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>C004178891 - MOLINA FUENTES DE MORE ELIZABETH</t>
+          <t>C004187618 - QUISPE DE PACHAS ANA MARIA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -21908,12 +21908,12 @@
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -21966,12 +21966,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>C004175861</t>
+          <t>C004178891</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>C004175861 - HERNANDEZ COELLO CARLOS JOHAO</t>
+          <t>C004178891 - MOLINA FUENTES DE MORE ELIZABETH</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -22060,12 +22060,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>C004187618</t>
+          <t>C004175861</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>C004187618 - QUISPE DE PACHAS ANA MARIA</t>
+          <t>C004175861 - HERNANDEZ COELLO CARLOS JOHAO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -22096,12 +22096,12 @@
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -22906,12 +22906,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>C004042194</t>
+          <t>C004028239</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>C004042194 - MOREYRA TAYPE BEATRIZ</t>
+          <t>C004028239 - DE LOS RIOS SALVATIERRA DIANA LIZBETH</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -22942,12 +22942,12 @@
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
@@ -23000,12 +23000,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C004028239</t>
+          <t>C004016311</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>C004028239 - DE LOS RIOS SALVATIERRA DIANA LIZBETH</t>
+          <t>C004016311 - HUACCAMAYTA ALMEYDA ELIZABETH CELESTE</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -23036,7 +23036,7 @@
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S247" t="inlineStr"/>
@@ -23094,12 +23094,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>C004016311</t>
+          <t>C004042194</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>C004016311 - HUACCAMAYTA ALMEYDA ELIZABETH CELESTE</t>
+          <t>C004042194 - MOREYRA TAYPE BEATRIZ</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -23130,17 +23130,17 @@
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S248" t="inlineStr"/>
@@ -23376,12 +23376,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>C001379004</t>
+          <t>C001423708</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>C001379004 - MUNANTE DE GONZALES CARMELA</t>
+          <t>C001423708 - MUNARES LOZA OLGA</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -23428,13 +23428,17 @@
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -23560,12 +23564,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>C001423708</t>
+          <t>C001379004</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>C001423708 - MUNARES LOZA OLGA</t>
+          <t>C001379004 - MUNANTE DE GONZALES CARMELA</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -23612,17 +23616,13 @@
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr"/>
       <c r="V253" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>

--- a/excel/distribuidora-aurelio-s-a-c_capacitaciones.xlsx
+++ b/excel/distribuidora-aurelio-s-a-c_capacitaciones.xlsx
@@ -864,12 +864,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C001288637</t>
+          <t>C001423708</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C001288637 - ESCOBAR ROJAS DE JAIME MARIA FELICITAS</t>
+          <t>C001423708 - MUNARES LOZA OLGA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -916,13 +916,17 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1052,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C001373321</t>
+          <t>C001288637</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C001373321 - HUAMAN FELIX CARMEN BARBARITA</t>
+          <t>C001288637 - ESCOBAR ROJAS DE JAIME MARIA FELICITAS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1084,12 +1088,12 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1100,17 +1104,13 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001423708</t>
+          <t>C001373321</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C001423708 - MUNARES LOZA OLGA</t>
+          <t>C001373321 - HUAMAN FELIX CARMEN BARBARITA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1178,12 +1178,12 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001476354</t>
+          <t>C001709591</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C001476354 - SANTIAGO CANCHARI TEODOMIRA ZONIA</t>
+          <t>C001709591 - RIOS PINEDO LUPE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C004016311</t>
+          <t>C001710992</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C004016311 - HUACCAMAYTA ALMEYDA ELIZABETH CELESTE</t>
+          <t>C001710992 - VILLEGAS YALLE LESLIE ANITA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1366,7 +1366,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1376,23 +1376,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1420,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C004028239</t>
+          <t>C001728535</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C004028239 - DE LOS RIOS SALVATIERRA DIANA LIZBETH</t>
+          <t>C001728535 - AURIS CHAVEZ DE CASTILLON ALICIA MARTINA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1465,7 +1461,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1518,12 +1514,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001728535</t>
+          <t>C001731574</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C001728535 - AURIS CHAVEZ DE CASTILLON ALICIA MARTINA</t>
+          <t>C001731574 - GARAY RAMOS GIANCARLO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1554,12 +1550,12 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1612,12 +1608,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001731574</t>
+          <t>C001476354</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C001731574 - GARAY RAMOS GIANCARLO</t>
+          <t>C001476354 - SANTIAGO CANCHARI TEODOMIRA ZONIA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1648,7 +1644,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1706,12 +1702,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001709591</t>
+          <t>C004243882</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C001709591 - RIOS PINEDO LUPE</t>
+          <t>C004243882 - ELIAS MUNAYCO MARIA GREGORIA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1747,7 +1743,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1800,12 +1796,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001710992</t>
+          <t>C004188867</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C001710992 - VILLEGAS YALLE LESLIE ANITA</t>
+          <t>C004188867 - ALMEYDA GUTIERREZ LUCILA MARGARITA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1852,13 +1848,17 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C004182921</t>
+          <t>C004178624</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C004182921 - GAGO CORDOVA FLOR EDITH</t>
+          <t>C004178624 - ROJAS OSCO SARITA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1926,7 +1926,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C004187411</t>
+          <t>C004182921</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C004187411 - PERALES TORRES BLANCA FLOR</t>
+          <t>C004182921 - GAGO CORDOVA FLOR EDITH</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2020,7 +2020,7 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C004188867</t>
+          <t>C004187411</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C004188867 - ALMEYDA GUTIERREZ LUCILA MARGARITA</t>
+          <t>C004187411 - PERALES TORRES BLANCA FLOR</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C004178624</t>
+          <t>C004170343</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C004178624 - ROJAS OSCO SARITA</t>
+          <t>C004170343 - PALACIOS CASTILLO MARJORI JANELA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2208,7 +2208,7 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2224,17 +2224,13 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2266,12 +2262,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C004170343</t>
+          <t>C004016311</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C004170343 - PALACIOS CASTILLO MARJORI JANELA</t>
+          <t>C004016311 - HUACCAMAYTA ALMEYDA ELIZABETH CELESTE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2302,7 +2298,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2312,19 +2308,23 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C004060561</t>
+          <t>C004028239</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>C004060561 - VELASQUEZ MONTEROLA JESUS ETEL</t>
+          <t>C004028239 - DE LOS RIOS SALVATIERRA DIANA LIZBETH</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2502,13 +2502,17 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2540,12 +2544,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C004060593</t>
+          <t>C004060561</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C004060593 - VALENTIN HUAMAN ROBERTO MARCELINO</t>
+          <t>C004060561 - VELASQUEZ MONTEROLA JESUS ETEL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2576,12 +2580,12 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2592,17 +2596,13 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2634,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C004243882</t>
+          <t>C004060593</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C004243882 - ELIAS MUNAYCO MARIA GREGORIA</t>
+          <t>C004060593 - VALENTIN HUAMAN ROBERTO MARCELINO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2670,12 +2670,12 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C001748707</t>
+          <t>C001518831</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C001748707 - GARCIA CHAVEZ SOLDER ALEX</t>
+          <t>C001518831 - CRISOSTOMO TALLA MABEL CRISTINA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2952,17 +2952,17 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001735118</t>
+          <t>C001499161</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C001735118 - CHAU CATACORA ARIANNA MARGOT</t>
+          <t>C001499161 - MORENO AVELLANEDA SUSAN ELIZABETH</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3042,12 +3042,12 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C001499161</t>
+          <t>C001748707</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C001499161 - MORENO AVELLANEDA SUSAN ELIZABETH</t>
+          <t>C001748707 - GARCIA CHAVEZ SOLDER ALEX</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3226,7 +3226,7 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3280,12 +3280,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C001518831</t>
+          <t>C001735118</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C001518831 - CRISOSTOMO TALLA MABEL CRISTINA</t>
+          <t>C001735118 - CHAU CATACORA ARIANNA MARGOT</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3316,7 +3316,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C004219844</t>
+          <t>C004059519</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C004219844 - LLIUYA LOPEZ NORMA ALICIA</t>
+          <t>C004059519 - NAPA ZAMBRANO PATTY YULIANA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C004215343</t>
+          <t>C004219844</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C004215343 - DE LA CRUZ DE LA CRUZ DE LUYO MELVI</t>
+          <t>C004219844 - LLIUYA LOPEZ NORMA ALICIA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C004059519</t>
+          <t>C004215343</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C004059519 - NAPA ZAMBRANO PATTY YULIANA</t>
+          <t>C004215343 - DE LA CRUZ DE LA CRUZ DE LUYO MELVI</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3615,12 +3615,12 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3652,12 +3652,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C004063304</t>
+          <t>C001371205</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C004063304 - AVALOS SANTOS MARIA ELENA</t>
+          <t>C001371205 - LLOCLLA CHAICO MARIA LUISA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3688,33 +3688,29 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3742,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C004093702</t>
+          <t>C001505052</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C004093702 - MISARE CABEZAS LINDA TEODORA</t>
+          <t>C001505052 - VELASQUEZ ALCA FIORELLA YESICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3787,7 +3783,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3840,12 +3836,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C004014163</t>
+          <t>C001450755</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C004014163 - PACHAS POLO NOEMI</t>
+          <t>C001450755 - RONCEROS ÑAÑEZ GIOVANA ELIZABETH</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3934,12 +3930,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C001746182</t>
+          <t>C001404404</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C001746182 - RAMIREZ HUAMAN MARIA ELENA</t>
+          <t>C001404404 - CULLANCO PEREZ EDALUZ LUZMILA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4024,12 +4020,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C001748711</t>
+          <t>C004093702</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C001748711 - ARANGO SOLDEVILLA PAOLA MARISOL</t>
+          <t>C004093702 - MISARE CABEZAS LINDA TEODORA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4060,12 +4056,12 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4076,13 +4072,17 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4114,12 +4114,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C001679429</t>
+          <t>C004063304</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C001679429 - ALMEYDA YATACO YOLANDA ESTHER</t>
+          <t>C004063304 - AVALOS SANTOS MARIA ELENA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4150,17 +4150,17 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
@@ -4171,12 +4171,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4208,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C001505052</t>
+          <t>C004014163</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C001505052 - VELASQUEZ ALCA FIORELLA YESICA</t>
+          <t>C004014163 - PACHAS POLO NOEMI</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C001450755</t>
+          <t>C001746182</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C001450755 - RONCEROS ÑAÑEZ GIOVANA ELIZABETH</t>
+          <t>C001746182 - RAMIREZ HUAMAN MARIA ELENA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4354,17 +4354,13 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4392,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001404404</t>
+          <t>C001748711</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C001404404 - CULLANCO PEREZ EDALUZ LUZMILA</t>
+          <t>C001748711 - ARANGO SOLDEVILLA PAOLA MARISOL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4432,12 +4428,12 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4486,12 +4482,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001371205</t>
+          <t>C001679429</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001371205 - LLOCLLA CHAICO MARIA LUISA</t>
+          <t>C001679429 - ALMEYDA YATACO YOLANDA ESTHER</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4538,13 +4534,17 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4576,12 +4576,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001114205</t>
+          <t>C004243890</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C001114205 - AURIS QUISPE SILVIA NANCY</t>
+          <t>C004243890 - PECHO ALMEYDA SANTA ROSA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001174840</t>
+          <t>C001114205</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C001174840 - FUENTES BERMEO ROSANA ALINDA</t>
+          <t>C001114205 - AURIS QUISPE SILVIA NANCY</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4886,7 +4886,7 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
@@ -4944,12 +4944,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C001369082</t>
+          <t>C001379004</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C001369082 - HUATTA MAMANI JUANA LUPE</t>
+          <t>C001379004 - MUNANTE DE GONZALES CARMELA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4996,17 +4996,13 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5038,12 +5034,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C001379004</t>
+          <t>C001376539</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C001379004 - MUNANTE DE GONZALES CARMELA</t>
+          <t>C001376539 - CARPIO JUNES JOSEFINA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5079,7 +5075,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5128,12 +5124,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C001376539</t>
+          <t>C001369082</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C001376539 - CARPIO JUNES JOSEFINA</t>
+          <t>C001369082 - HUATTA MAMANI JUANA LUPE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5180,13 +5176,17 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -5218,12 +5218,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001644118</t>
+          <t>C001174840</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C001644118 - MARCOS PILPE SHIRLE EDITH</t>
+          <t>C001174840 - FUENTES BERMEO ROSANA ALINDA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5254,12 +5254,12 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001495761</t>
+          <t>C001644118</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C001495761 - GARCIA TELLO VICTORIA</t>
+          <t>C001644118 - MARCOS PILPE SHIRLE EDITH</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5348,12 +5348,12 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001450198</t>
+          <t>C001531013</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C001450198 - SALVADOR ALMEYDA MARITZA MAXIMILIANA</t>
+          <t>C001531013 - TORRES ORTIZ GIOVANNA DEL PILAR</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5442,7 +5442,7 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -5458,17 +5458,13 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5496,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001487012</t>
+          <t>C001450198</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C001487012 - CHACALIAZA CHACALTANA MARIA DEL CARMEN</t>
+          <t>C001450198 - SALVADOR ALMEYDA MARITZA MAXIMILIANA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5536,12 +5532,12 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5594,12 +5590,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C001531013</t>
+          <t>C001487012</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C001531013 - TORRES ORTIZ GIOVANNA DEL PILAR</t>
+          <t>C001487012 - CHACALIAZA CHACALTANA MARIA DEL CARMEN</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5635,7 +5631,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5646,13 +5642,17 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5684,12 +5684,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C004212960</t>
+          <t>C001495761</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C004212960 - CHANCA DE LA MATA SABINA</t>
+          <t>C001495761 - GARCIA TELLO VICTORIA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5720,12 +5720,12 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C004243890</t>
+          <t>C004177967</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C004243890 - PECHO ALMEYDA SANTA ROSA</t>
+          <t>C004177967 - TORRES RAMOS MIRTHA JUDITH</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5809,17 +5809,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5830,17 +5834,13 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5872,12 +5872,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C004177967</t>
+          <t>C004178891</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C004177967 - TORRES RAMOS MIRTHA JUDITH</t>
+          <t>C004178891 - MOLINA FUENTES DE MORE ELIZABETH</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5903,16 +5903,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -5928,13 +5924,17 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C004178891</t>
+          <t>C004175861</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C004178891 - MOLINA FUENTES DE MORE ELIZABETH</t>
+          <t>C004175861 - HERNANDEZ COELLO CARLOS JOHAO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6002,7 +6002,7 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C004175861</t>
+          <t>C004212960</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C004175861 - HERNANDEZ COELLO CARLOS JOHAO</t>
+          <t>C004212960 - CHANCA DE LA MATA SABINA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C004009166</t>
+          <t>C004014363</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C004009166 - TORRES HILARIO JOEL MARTIN</t>
+          <t>C004014363 - SANCHEZ VALENZUELA LUZ URIETA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6190,7 +6190,7 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C004014363</t>
+          <t>C004009166</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C004014363 - SANCHEZ VALENZUELA LUZ URIETA</t>
+          <t>C004009166 - TORRES HILARIO JOEL MARTIN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6280,7 +6280,7 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C001215499</t>
+          <t>C004174277</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C001215499 - APOLAYA GONZALES ANGELICA MILAGROS</t>
+          <t>C004174277 - ORELLANA ATUNCAR EDUARDO JESUS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001414285</t>
+          <t>C004161274</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C001414285 - GUILLEN MENDIZ CRISTINA BLANCA</t>
+          <t>C004161274 - GUERRA MARTINEZ SILVESTRE PAULINO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S65" t="inlineStr"/>
@@ -6522,12 +6522,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C001391394</t>
+          <t>C004069758</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C001391394 - FARFAN CHIRA MARILU GIOVANA</t>
+          <t>C004069758 - CONDE JACOBO ROXANA MARGARITA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C000960971</t>
+          <t>C004101162</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C000960971 - TICONA URRUCHI SOCORRO MERCEDES</t>
+          <t>C004101162 - CRISTOBAL PALOMINO SONIA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6668,17 +6668,13 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6710,12 +6706,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C001493339</t>
+          <t>C004014318</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C001493339 - SALVADOR MENESES ROSA HILDA</t>
+          <t>C004014318 - URIONDO YATACO GLADYS AMALIA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6756,19 +6752,23 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C001504560</t>
+          <t>C001740943</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>C001504560 - MAGALLANES MATEO MARIA ANGELICA</t>
+          <t>C001740943 - ROJAS AVALOS JOSE ORLANDO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6836,7 +6836,7 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -6857,12 +6857,12 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C001506187</t>
+          <t>C001533081</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C001506187 - CAYCHO FLORES DE GUTIERREZ LUCILA DORA</t>
+          <t>C001533081 - PACHAS FELIX VIVIANA MARILU</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6930,7 +6930,7 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -6946,17 +6946,13 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6984,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C001513764</t>
+          <t>C001493339</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C001513764 - TASAYCO PACHAS CARLOS ALBERTO</t>
+          <t>C001493339 - SALVADOR MENESES ROSA HILDA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7034,7 +7030,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S71" t="inlineStr"/>
@@ -7078,12 +7074,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C001530326</t>
+          <t>C001414285</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C001530326 - MARCELO GONZALES MIRTHA</t>
+          <t>C001414285 - GUILLEN MENDIZ CRISTINA BLANCA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7172,12 +7168,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001533081</t>
+          <t>C001504560</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C001533081 - PACHAS FELIX VIVIANA MARILU</t>
+          <t>C001504560 - MAGALLANES MATEO MARIA ANGELICA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7208,7 +7204,7 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -7224,13 +7220,17 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C004174277</t>
+          <t>C001506187</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C004174277 - ORELLANA ATUNCAR EDUARDO JESUS</t>
+          <t>C001506187 - CAYCHO FLORES DE GUTIERREZ LUCILA DORA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7356,12 +7356,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C004101162</t>
+          <t>C001513764</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C004101162 - CRISTOBAL PALOMINO SONIA</t>
+          <t>C001513764 - TASAYCO PACHAS CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7392,7 +7392,7 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C004161274</t>
+          <t>C001530326</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C004161274 - GUERRA MARTINEZ SILVESTRE PAULINO</t>
+          <t>C001530326 - MARCELO GONZALES MIRTHA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S76" t="inlineStr"/>
@@ -7540,12 +7540,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001740943</t>
+          <t>C000960971</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C001740943 - ROJAS AVALOS JOSE ORLANDO</t>
+          <t>C000960971 - TICONA URRUCHI SOCORRO MERCEDES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7597,12 +7597,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7634,12 +7634,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C004069758</t>
+          <t>C001215499</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C004069758 - CONDE JACOBO ROXANA MARGARITA</t>
+          <t>C001215499 - APOLAYA GONZALES ANGELICA MILAGROS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7670,7 +7670,7 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C004014318</t>
+          <t>C001391394</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C004014318 - URIONDO YATACO GLADYS AMALIA</t>
+          <t>C001391394 - FARFAN CHIRA MARILU GIOVANA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7764,12 +7764,12 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7785,12 +7785,12 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C001493102</t>
+          <t>C000957354</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C001493102 - CANCHERO CURACA JULIA ALEJANDRINA</t>
+          <t>C000957354 - DE LA CRUZ BOHORQUEZ ROSA VIRGINIA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7950,19 +7950,35 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Agregar productos al carrito</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7994,12 +8010,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C000957354</t>
+          <t>C000961480</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>C000957354 - DE LA CRUZ BOHORQUEZ ROSA VIRGINIA</t>
+          <t>C000961480 - COLQUEPISCO FLORES JUANA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8035,7 +8051,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -8088,12 +8104,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C000961480</t>
+          <t>C001716816</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>C000961480 - COLQUEPISCO FLORES JUANA</t>
+          <t>C001716816 - MARTINEZ CANDIOTTE JOHAN JOHNSON</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8124,12 +8140,12 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -8145,12 +8161,12 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8188,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8182,17 +8198,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C001716816</t>
+          <t>C001493102</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>C001716816 - MARTINEZ CANDIOTTE JOHAN JOHNSON</t>
+          <t>C001493102 - CANCHERO CURACA JULIA ALEJANDRINA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
@@ -8205,7 +8221,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8216,35 +8232,19 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Poco dispuesto</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -8648,12 +8648,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C004036901</t>
+          <t>C004028243</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>C004036901 - CANCHERO CURACA BERTHA ALEJANDRINA</t>
+          <t>C004028243 - ROJAS CUSIPUMA HERLINDA YESENIA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8684,12 +8684,12 @@
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8700,13 +8700,17 @@
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9016,12 +9020,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C004028243</t>
+          <t>C004036901</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C004028243 - ROJAS CUSIPUMA HERLINDA YESENIA</t>
+          <t>C004036901 - CANCHERO CURACA BERTHA ALEJANDRINA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9052,12 +9056,12 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -9068,17 +9072,13 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C004001775</t>
+          <t>C001516754</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>C004001775 - CUSIPUMA LAZA YANDEL VALERIO</t>
+          <t>C001516754 - DE LA MATTA TORNERO NOEMI OLIVA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C001742520</t>
+          <t>C001716813</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C001742520 - REYES RAMOS DIANA</t>
+          <t>C001716813 - LINO GARCIA DARLINE FERNANDA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9240,7 +9240,7 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9298,12 +9298,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C001716813</t>
+          <t>C001704992</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>C001716813 - LINO GARCIA DARLINE FERNANDA</t>
+          <t>C001704992 - VASQUEZ CHUQUISPUMA EVELYN</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9334,7 +9334,7 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -9355,12 +9355,12 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C001704992</t>
+          <t>C004001775</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C001704992 - VASQUEZ CHUQUISPUMA EVELYN</t>
+          <t>C004001775 - CUSIPUMA LAZA YANDEL VALERIO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9428,12 +9428,12 @@
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9486,12 +9486,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C001516754</t>
+          <t>C001742520</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C001516754 - DE LA MATTA TORNERO NOEMI OLIVA</t>
+          <t>C001742520 - REYES RAMOS DIANA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9522,12 +9522,12 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -9580,12 +9580,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C001629771</t>
+          <t>C004013408</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C001629771 - ROJAS RODRIGUEZ MARIA ESTHER</t>
+          <t>C004013408 - QUISPE QUISPE ELIZABETH WENDY</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9674,12 +9674,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C001530822</t>
+          <t>C001748704</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>C001530822 - REYES QUISPE SANTA ANGELICA</t>
+          <t>C001748704 - ASTORAYME DE QUISPE MARIA DEL CARMEN</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9710,7 +9710,7 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C001489307</t>
+          <t>C001732725</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>C001489307 - SOLORZANO MITMA RICHAR</t>
+          <t>C001732725 - LANDEO FLORES YORFA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9820,17 +9820,13 @@
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9862,12 +9858,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>C001504541</t>
+          <t>C001629771</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>C001504541 - CARBAJAL ORTIZ MARIA LILIA</t>
+          <t>C001629771 - ROJAS RODRIGUEZ MARIA ESTHER</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9898,7 +9894,7 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -9956,12 +9952,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>C001511764</t>
+          <t>C001405847</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>C001511764 - ASTORAYME BENDEZU CINTHIA YESSENIA</t>
+          <t>C001405847 - DIAZ VELASQUEZ DE SESSAREGO MARIA PIEDAD</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9992,12 +9988,12 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -10008,17 +10004,13 @@
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10050,12 +10042,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>C001165037</t>
+          <t>C001489307</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>C001165037 - QUIROZ VERA ROSA ELIZABETH</t>
+          <t>C001489307 - SOLORZANO MITMA RICHAR</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -10081,11 +10073,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -10148,12 +10136,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>C001168647</t>
+          <t>C001530822</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>C001168647 - MEZA BENDEZU ROCIO RENE</t>
+          <t>C001530822 - REYES QUISPE SANTA ANGELICA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10184,7 +10172,7 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -10242,12 +10230,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>C001405847</t>
+          <t>C001495385</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>C001405847 - DIAZ VELASQUEZ DE SESSAREGO MARIA PIEDAD</t>
+          <t>C001495385 - AYASTA FELIX NORMA ZOILA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10278,12 +10266,12 @@
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -10332,12 +10320,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>C001495385</t>
+          <t>C001168647</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>C001495385 - AYASTA FELIX NORMA ZOILA</t>
+          <t>C001168647 - MEZA BENDEZU ROCIO RENE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10373,7 +10361,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -10384,13 +10372,17 @@
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10422,12 +10414,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>C001732725</t>
+          <t>C004240083</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>C001732725 - LANDEO FLORES YORFA</t>
+          <t>C004240083 - SANCA FLOREZ JUDITH</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10474,13 +10466,17 @@
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10512,12 +10508,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>C004013408</t>
+          <t>C004210148</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>C004013408 - QUISPE QUISPE ELIZABETH WENDY</t>
+          <t>C004210148 - PEREZ DE SANCHEZ JONNY HILDA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10553,7 +10549,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -10569,12 +10565,12 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10606,12 +10602,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>C001748704</t>
+          <t>C004176093</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>C001748704 - ASTORAYME DE QUISPE MARIA DEL CARMEN</t>
+          <t>C004176093 - ZAMBRANO CASTILLA GYLARY LAILA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10642,17 +10638,17 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S110" t="inlineStr"/>
@@ -10700,12 +10696,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C004240083</t>
+          <t>C001738163</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>C004240083 - SANCA FLOREZ JUDITH</t>
+          <t>C001738163 - GUTIERREZ ROJAS CLEMENTINA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10736,12 +10732,12 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -10752,17 +10748,13 @@
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10794,12 +10786,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>C004210148</t>
+          <t>C001653241</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>C004210148 - PEREZ DE SANCHEZ JONNY HILDA</t>
+          <t>C001653241 - BOLO MINAYA JUANA JULIA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10835,7 +10827,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10888,12 +10880,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>C001541280</t>
+          <t>C001504541</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C001541280 - VIVANCO GARCIA MARIBEL</t>
+          <t>C001504541 - CARBAJAL ORTIZ MARIA LILIA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10924,7 +10916,7 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -10982,12 +10974,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>C001738163</t>
+          <t>C001511764</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>C001738163 - GUTIERREZ ROJAS CLEMENTINA</t>
+          <t>C001511764 - ASTORAYME BENDEZU CINTHIA YESSENIA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -11018,12 +11010,12 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -11034,13 +11026,17 @@
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11072,12 +11068,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>C001653241</t>
+          <t>C001541280</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>C001653241 - BOLO MINAYA JUANA JULIA</t>
+          <t>C001541280 - VIVANCO GARCIA MARIBEL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -11113,7 +11109,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -11166,12 +11162,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C004061401</t>
+          <t>C004007837</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>C004061401 - FIGUEROA CASTILLA WILLIAM JAVIER</t>
+          <t>C004007837 - QUISPE CRUZ SONIA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -11202,7 +11198,7 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -11223,12 +11219,12 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -11260,12 +11256,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C004007837</t>
+          <t>C004061401</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C004007837 - QUISPE CRUZ SONIA</t>
+          <t>C004061401 - FIGUEROA CASTILLA WILLIAM JAVIER</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -11296,7 +11292,7 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -11317,12 +11313,12 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11354,12 +11350,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C004176093</t>
+          <t>C004095681</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>C004176093 - ZAMBRANO CASTILLA GYLARY LAILA</t>
+          <t>C004095681 - PACHAS PACHAS MARIA YSABEL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11400,7 +11396,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S118" t="inlineStr"/>
@@ -11448,12 +11444,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>C004095681</t>
+          <t>C001165037</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>C004095681 - PACHAS PACHAS MARIA YSABEL</t>
+          <t>C001165037 - QUIROZ VERA ROSA ELIZABETH</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -11479,12 +11475,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>C004178904</t>
+          <t>C001733927</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>C004178904 - BELLEZA QUISPE ROSARIO PATRICIA</t>
+          <t>C001733927 - RODRIGUEZ PALOMINO LESLY JULISSA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -13909,12 +13909,12 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -13946,12 +13946,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>C004180920</t>
+          <t>C004178904</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>C004180920 - ORIHUELA VALENTIN EDELMIRA VICENTA</t>
+          <t>C004178904 - BELLEZA QUISPE ROSARIO PATRICIA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -14040,12 +14040,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>C001550279</t>
+          <t>C004180920</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>C001550279 - BALBUENA HUAMAN GUISELLA MARGOT</t>
+          <t>C004180920 - ORIHUELA VALENTIN EDELMIRA VICENTA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -14134,12 +14134,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>C001374770</t>
+          <t>C001550279</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>C001374770 - OCHOA HERRERA SOFIA VANESSA</t>
+          <t>C001550279 - BALBUENA HUAMAN GUISELLA MARGOT</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -14170,7 +14170,7 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S148" t="inlineStr"/>
@@ -14191,12 +14191,12 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -14228,12 +14228,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>C001160082</t>
+          <t>C001374770</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>C001160082 - TORRES SIERRA SARA DEL ROSARIO</t>
+          <t>C001374770 - OCHOA HERRERA SOFIA VANESSA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -14264,7 +14264,7 @@
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S149" t="inlineStr"/>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>C001158905</t>
+          <t>C001160082</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>C001158905 - DIAZ PEREZ ELIZABETH</t>
+          <t>C001160082 - TORRES SIERRA SARA DEL ROSARIO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -14358,7 +14358,7 @@
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -14416,12 +14416,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>C000957808</t>
+          <t>C001158905</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>C000957808 - NAPANGA PEREZ BALBINA ISIDORA</t>
+          <t>C001158905 - DIAZ PEREZ ELIZABETH</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -14510,12 +14510,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>C000960458</t>
+          <t>C000957808</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>C000960458 - VERA NUNEZ NORMA GREGORIA</t>
+          <t>C000957808 - NAPANGA PEREZ BALBINA ISIDORA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -14546,7 +14546,7 @@
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -14604,12 +14604,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>C001086594</t>
+          <t>C000960458</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>C001086594 - RAMOS CAHUANA SONIA ISABEL</t>
+          <t>C000960458 - VERA NUNEZ NORMA GREGORIA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -14640,7 +14640,7 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -14661,12 +14661,12 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -14698,12 +14698,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C001159487</t>
+          <t>C001086594</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>C001159487 - ESPINO LOZA OLIVIA</t>
+          <t>C001086594 - RAMOS CAHUANA SONIA ISABEL</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14750,13 +14750,17 @@
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U154" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -14788,12 +14792,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>C004037620</t>
+          <t>C001159487</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>C004037620 - CAHUAPAS TORNERO MARILU NOELIA</t>
+          <t>C001159487 - ESPINO LOZA OLIVIA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -14824,12 +14828,12 @@
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -14840,17 +14844,13 @@
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -14882,12 +14882,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>C004038251</t>
+          <t>C004037620</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>C004038251 - MACHUCA PALOMINO EDITH ANICETA</t>
+          <t>C004037620 - CAHUAPAS TORNERO MARILU NOELIA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -14934,13 +14934,17 @@
       <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U156" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -14972,12 +14976,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>C004016284</t>
+          <t>C004038251</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>C004016284 - QUINCHO QUINCHO MELCHORA FELICIA</t>
+          <t>C004038251 - MACHUCA PALOMINO EDITH ANICETA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -15024,17 +15028,13 @@
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>C004030149</t>
+          <t>C004016284</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>C004030149 - REYMUNDO PARIONA TEOFILA</t>
+          <t>C004016284 - QUINCHO QUINCHO MELCHORA FELICIA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -15102,7 +15102,7 @@
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -15160,12 +15160,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>C004065232</t>
+          <t>C004030149</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>C004065232 - AGUADO LOPEZ CHAI TIODOLINDA</t>
+          <t>C004030149 - REYMUNDO PARIONA TEOFILA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -15196,7 +15196,7 @@
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S159" t="inlineStr"/>
@@ -15254,12 +15254,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>C004008021</t>
+          <t>C004065232</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>C004008021 - HUAMAN FERNANDEZ LUIS JAIRO</t>
+          <t>C004065232 - AGUADO LOPEZ CHAI TIODOLINDA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -15306,13 +15306,17 @@
       <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U160" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15348,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>C001733927</t>
+          <t>C004008021</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>C001733927 - RODRIGUEZ PALOMINO LESLY JULISSA</t>
+          <t>C004008021 - HUAMAN FERNANDEZ LUIS JAIRO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -15385,28 +15389,24 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -15986,12 +15986,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>C004013473</t>
+          <t>C001532127</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>C004013473 - TASAYCO SARAVIA WALTER</t>
+          <t>C001532127 - TASAYCO SITU ENZO GIUSEPPE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S168" t="inlineStr"/>
@@ -16080,12 +16080,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>C001532127</t>
+          <t>C001556308</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>C001532127 - TASAYCO SITU ENZO GIUSEPPE</t>
+          <t>C001556308 - HUISA HUARACA MERCEDES</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -16137,12 +16137,12 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -16174,12 +16174,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>C001556308</t>
+          <t>C001493327</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>C001556308 - HUISA HUARACA MERCEDES</t>
+          <t>C001493327 - OLIVERO TORRES GLORIA YSABEL</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -16210,12 +16210,12 @@
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -16268,12 +16268,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>C001493327</t>
+          <t>C004013473</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>C001493327 - OLIVERO TORRES GLORIA YSABEL</t>
+          <t>C004013473 - TASAYCO SARAVIA WALTER</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -16304,7 +16304,7 @@
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S171" t="inlineStr"/>
@@ -16325,12 +16325,12 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -18144,12 +18144,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>C001379080</t>
+          <t>C001427276</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>C001379080 - MORAN DE GONZALES ROSA MARIA</t>
+          <t>C001427276 - SALAZAR ROJAS FLOR DE MARIA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S191" t="inlineStr"/>
@@ -18201,12 +18201,12 @@
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -18238,12 +18238,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>C001427276</t>
+          <t>C001430224</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>C001427276 - SALAZAR ROJAS FLOR DE MARIA</t>
+          <t>C001430224 - LEVANO RAMOS MAGALLY ROCIO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -18279,12 +18279,12 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S192" t="inlineStr"/>
@@ -18295,12 +18295,12 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18332,12 +18332,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>C001430224</t>
+          <t>C001379080</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>C001430224 - LEVANO RAMOS MAGALLY ROCIO</t>
+          <t>C001379080 - MORAN DE GONZALES ROSA MARIA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -18373,7 +18373,7 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -18614,12 +18614,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>C004032632</t>
+          <t>C004049669</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>C004032632 - MAGALLANES QUIROZ DE TASAYCO CARMEN LUIS</t>
+          <t>C004049669 - HERRERA AGUIRRE CINDY</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -18655,12 +18655,12 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S196" t="inlineStr"/>
@@ -18671,12 +18671,12 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18708,12 +18708,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>C004049669</t>
+          <t>C004032632</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>C004049669 - HERRERA AGUIRRE CINDY</t>
+          <t>C004032632 - MAGALLANES QUIROZ DE TASAYCO CARMEN LUIS</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -18749,12 +18749,12 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S197" t="inlineStr"/>
@@ -18765,12 +18765,12 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -19554,12 +19554,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>C001551656</t>
+          <t>C001307050</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>C001551656 - PIZARRO BAYLETTI CRISTIAN SALVADOR</t>
+          <t>C001307050 - QUISPE NORMA BERNARDINA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -19590,7 +19590,7 @@
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
@@ -19611,12 +19611,12 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -19648,12 +19648,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>C001556504</t>
+          <t>C001541713</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>C001556504 - SALVATIERRA MACHUCA KARIN ELIANA</t>
+          <t>C001541713 - CANALES AYLLON RUTH LADY</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -19684,7 +19684,7 @@
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
@@ -19742,12 +19742,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>C001541713</t>
+          <t>C001551656</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>C001541713 - CANALES AYLLON RUTH LADY</t>
+          <t>C001551656 - PIZARRO BAYLETTI CRISTIAN SALVADOR</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
@@ -19799,12 +19799,12 @@
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -19836,12 +19836,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>C001497344</t>
+          <t>C001556504</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>C001497344 - EMPRESA COMERCIAL DISTRIBUIDORA H &amp; C S.</t>
+          <t>C001556504 - SALVATIERRA MACHUCA KARIN ELIANA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -19872,7 +19872,7 @@
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -19882,7 +19882,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S209" t="inlineStr"/>
@@ -19930,12 +19930,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>C001307050</t>
+          <t>C001628870</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>C001307050 - QUISPE NORMA BERNARDINA</t>
+          <t>C001628870 - ANDRADE DE LA CRUZ ALDO ANDRES</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -19966,12 +19966,12 @@
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
@@ -19982,17 +19982,13 @@
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20024,12 +20020,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C004166807</t>
+          <t>C001497344</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>C004166807 - CARBAJAL LLIUYA LUZ EVELYN</t>
+          <t>C001497344 - EMPRESA COMERCIAL DISTRIBUIDORA H &amp; C S.</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -20065,12 +20061,12 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="S211" t="inlineStr"/>
@@ -20118,12 +20114,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C004049158</t>
+          <t>C004166807</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>C004049158 - HILARION HUAYLLA JOSE LUIS</t>
+          <t>C004166807 - CARBAJAL LLIUYA LUZ EVELYN</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -20154,7 +20150,7 @@
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -20170,13 +20166,17 @@
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U212" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -20208,12 +20208,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>C004028744</t>
+          <t>C004049158</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>C004028744 - ABURTO YATACO ALEX ROBERTO</t>
+          <t>C004049158 - HILARION HUAYLLA JOSE LUIS</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -20244,12 +20244,12 @@
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
@@ -20260,17 +20260,13 @@
       <c r="S213" t="inlineStr"/>
       <c r="T213" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20302,12 +20298,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>C004001810</t>
+          <t>C004028744</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>C004001810 - CAYCHO HUAMAN OLGA LIDIA</t>
+          <t>C004028744 - ABURTO YATACO ALEX ROBERTO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -20338,7 +20334,7 @@
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
@@ -20396,12 +20392,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>C004007835</t>
+          <t>C004001810</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>C004007835 - HUASASQUICHE SALAS SANTIAGO FELIPE</t>
+          <t>C004001810 - CAYCHO HUAMAN OLGA LIDIA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -20432,7 +20428,7 @@
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -20453,12 +20449,12 @@
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -20490,12 +20486,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>C001723032</t>
+          <t>C004007835</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>C001723032 - QUISPE PALOMINO EDDIE MERINIYES</t>
+          <t>C004007835 - HUASASQUICHE SALAS SANTIAGO FELIPE</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -20526,7 +20522,7 @@
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -20536,7 +20532,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S216" t="inlineStr"/>
@@ -20547,12 +20543,12 @@
       </c>
       <c r="U216" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V216" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -20584,12 +20580,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>C001628870</t>
+          <t>C001723032</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>C001628870 - ANDRADE DE LA CRUZ ALDO ANDRES</t>
+          <t>C001723032 - QUISPE PALOMINO EDDIE MERINIYES</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -20620,7 +20616,7 @@
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -20630,19 +20626,23 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U217" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -20956,12 +20956,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C004169879</t>
+          <t>C004094381</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>C004169879 - CHAVEZ CAHUANA LILI ZUNILDA</t>
+          <t>C004094381 - TORRES RIVAS DAYANA KAREN</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -20992,17 +20992,17 @@
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="S221" t="inlineStr"/>
@@ -21050,12 +21050,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>C004172212</t>
+          <t>C004169879</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>C004172212 - MORALES ROMERO SILVIA ROSARIO</t>
+          <t>C004169879 - CHAVEZ CAHUANA LILI ZUNILDA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -21086,7 +21086,7 @@
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -21144,12 +21144,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>C004060561</t>
+          <t>C004172212</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>C004060561 - VELASQUEZ MONTEROLA JESUS ETEL</t>
+          <t>C004172212 - MORALES ROMERO SILVIA ROSARIO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -21180,12 +21180,12 @@
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -21196,13 +21196,17 @@
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U223" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21234,12 +21238,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>C004094381</t>
+          <t>C004060561</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>C004094381 - TORRES RIVAS DAYANA KAREN</t>
+          <t>C004060561 - VELASQUEZ MONTEROLA JESUS ETEL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -21280,23 +21284,19 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -21704,12 +21704,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>C001728535</t>
+          <t>C001737256</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>C001728535 - AURIS CHAVEZ DE CASTILLON ALICIA MARTINA</t>
+          <t>C001737256 - RAMOS ROMERO MARILUZ LILIANA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -21740,7 +21740,7 @@
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
@@ -21798,12 +21798,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>C001737256</t>
+          <t>C001728535</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>C001737256 - RAMOS ROMERO MARILUZ LILIANA</t>
+          <t>C001728535 - AURIS CHAVEZ DE CASTILLON ALICIA MARTINA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -21834,7 +21834,7 @@
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
@@ -22080,12 +22080,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>C001551841</t>
+          <t>C001522451</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>C001551841 - TASAYCO MAGALLANES YEISY MEDALIT</t>
+          <t>C001522451 - CARCAMO DE ROJAS DACIANA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -22116,7 +22116,7 @@
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -22174,12 +22174,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>C001522451</t>
+          <t>C001551841</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>C001522451 - CARCAMO DE ROJAS DACIANA</t>
+          <t>C001551841 - TASAYCO MAGALLANES YEISY MEDALIT</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -22210,7 +22210,7 @@
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
@@ -22268,12 +22268,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>C001365658</t>
+          <t>C001517282</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>C001365658 - PAUCAR CRISOSTOMO ZENAIDA SEREGIA</t>
+          <t>C001517282 - CLAROS FELIX JESSICA DEL ROSARIO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -22304,12 +22304,12 @@
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>C001454048</t>
+          <t>C001365658</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>C001454048 - VILCAPUMA YAURI MARLENE FIORELLA</t>
+          <t>C001365658 - PAUCAR CRISOSTOMO ZENAIDA SEREGIA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -22398,7 +22398,7 @@
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
@@ -22419,12 +22419,12 @@
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V236" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22456,12 +22456,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>C001498029</t>
+          <t>C001454048</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>C001498029 - CASTILLON HERRERA KLEYBER YONZON</t>
+          <t>C001454048 - VILCAPUMA YAURI MARLENE FIORELLA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -22492,7 +22492,7 @@
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
@@ -22513,12 +22513,12 @@
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -22550,12 +22550,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>C001517282</t>
+          <t>C001498029</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>C001517282 - CLAROS FELIX JESSICA DEL ROSARIO</t>
+          <t>C001498029 - CASTILLON HERRERA KLEYBER YONZON</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -22591,7 +22591,7 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -22738,12 +22738,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>C001490980</t>
+          <t>C000957338</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>C001490980 - ROJAS ATUNCAR VICTOR JAVIER</t>
+          <t>C000957338 - ATUNCAR CASTA EDA ROSA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -22769,16 +22769,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
@@ -22788,7 +22784,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S240" t="inlineStr"/>
@@ -22836,12 +22832,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>C001555062</t>
+          <t>C000961008</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>C001555062 - CHAVEZ PRADA DE CANELO NELLY VICTORIA</t>
+          <t>C000961008 - ALMEYDA MATIAS HUGO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -22872,7 +22868,7 @@
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
@@ -22882,7 +22878,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S241" t="inlineStr"/>
@@ -22930,12 +22926,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>C001555703</t>
+          <t>C001477089</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>C001555703 - ROJAS DE LA CRUZ JUAN ARTURO</t>
+          <t>C001477089 - VIDALON NOA DELIA BERTHA</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -22966,17 +22962,17 @@
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S242" t="inlineStr"/>
@@ -22987,12 +22983,12 @@
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -23024,12 +23020,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>C001477089</t>
+          <t>C001490980</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>C001477089 - VIDALON NOA DELIA BERTHA</t>
+          <t>C001490980 - ROJAS ATUNCAR VICTOR JAVIER</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -23055,7 +23051,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
@@ -23065,7 +23065,7 @@
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
@@ -23118,12 +23118,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>C001403893</t>
+          <t>C001555062</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>C001403893 - SALCEDO FALCONI IDA PAULINA</t>
+          <t>C001555062 - CHAVEZ PRADA DE CANELO NELLY VICTORIA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -23154,7 +23154,7 @@
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
@@ -23164,7 +23164,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S244" t="inlineStr"/>
@@ -23212,12 +23212,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>C001369944</t>
+          <t>C001555703</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>C001369944 - FUENTES SALVADOR MARIA BLANCA ESTHER</t>
+          <t>C001555703 - ROJAS DE LA CRUZ JUAN ARTURO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -23258,7 +23258,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S245" t="inlineStr"/>
@@ -23269,12 +23269,12 @@
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -23306,12 +23306,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>C001370197</t>
+          <t>C001403893</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>C001370197 - DE LA CRUZ DE GENTILLE DORIS GUILLERMINA</t>
+          <t>C001403893 - SALCEDO FALCONI IDA PAULINA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -23342,7 +23342,7 @@
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
@@ -23400,12 +23400,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C000957338</t>
+          <t>C001369944</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>C000957338 - ATUNCAR CASTA EDA ROSA</t>
+          <t>C001369944 - FUENTES SALVADOR MARIA BLANCA ESTHER</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -23494,12 +23494,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>C000961008</t>
+          <t>C001370197</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>C000961008 - ALMEYDA MATIAS HUGO</t>
+          <t>C001370197 - DE LA CRUZ DE GENTILLE DORIS GUILLERMINA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -23530,7 +23530,7 @@
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
@@ -24242,12 +24242,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>C004242613</t>
+          <t>C004179159</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>C004242613 - AVALOS ALMEYDA GLADYS ROSA</t>
+          <t>C004179159 - SILVA VILCHERREZ CARITO ELIZABETH</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -24278,7 +24278,7 @@
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
@@ -24288,7 +24288,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S256" t="inlineStr"/>
@@ -24336,12 +24336,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>C004179159</t>
+          <t>C004058896</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>C004179159 - SILVA VILCHERREZ CARITO ELIZABETH</t>
+          <t>C004058896 - CARPIO PACHAS LUISA NELLY</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -24372,17 +24372,17 @@
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S257" t="inlineStr"/>
@@ -24393,12 +24393,12 @@
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -24524,12 +24524,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>C004058896</t>
+          <t>C004242613</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>C004058896 - CARPIO PACHAS LUISA NELLY</t>
+          <t>C004242613 - AVALOS ALMEYDA GLADYS ROSA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -24565,7 +24565,7 @@
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -24581,12 +24581,12 @@
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24618,12 +24618,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>C004059519</t>
+          <t>C004014168</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>C004059519 - NAPA ZAMBRANO PATTY YULIANA</t>
+          <t>C004014168 - HUARANCA CUSIPUMA OLIVA ERICA</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -24654,12 +24654,12 @@
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -24712,12 +24712,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>C004014168</t>
+          <t>C004059519</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>C004014168 - HUARANCA CUSIPUMA OLIVA ERICA</t>
+          <t>C004059519 - NAPA ZAMBRANO PATTY YULIANA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -24748,12 +24748,12 @@
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -24998,12 +24998,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>C001653300</t>
+          <t>C004188867</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>C001653300 - CCAPA CRUZ JUANA</t>
+          <t>C004188867 - ALMEYDA GUTIERREZ LUCILA MARGARITA</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -25039,7 +25039,7 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -25055,12 +25055,12 @@
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V264" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25092,12 +25092,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>C000957551</t>
+          <t>C004014163</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>C000957551 - RAMIREZ DE MATTA ESPERANZA</t>
+          <t>C004014163 - PACHAS POLO NOEMI</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -25133,7 +25133,7 @@
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -25186,12 +25186,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>C000961456</t>
+          <t>C000956336</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>C000961456 - SUAREZ DE WONG VERONICA ISABEL</t>
+          <t>C000956336 - SULLCAPUMA DE VARGAS CIRILA ROSA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -25222,17 +25222,17 @@
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S266" t="inlineStr"/>
@@ -25243,12 +25243,12 @@
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25280,12 +25280,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>C000960371</t>
+          <t>C000961456</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>C000960371 - HUASASQUICHE ASTORAYME VILMA</t>
+          <t>C000961456 - SUAREZ DE WONG VERONICA ISABEL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -25374,12 +25374,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>C000956336</t>
+          <t>C000960371</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>C000956336 - SULLCAPUMA DE VARGAS CIRILA ROSA</t>
+          <t>C000960371 - HUASASQUICHE ASTORAYME VILMA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -25410,17 +25410,17 @@
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S268" t="inlineStr"/>
@@ -25431,12 +25431,12 @@
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V268" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25468,12 +25468,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>C004188867</t>
+          <t>C000957551</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>C004188867 - ALMEYDA GUTIERREZ LUCILA MARGARITA</t>
+          <t>C000957551 - RAMIREZ DE MATTA ESPERANZA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -25656,12 +25656,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>C001319626</t>
+          <t>C001526666</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>C001319626 - TUPAC VILCAPUMA MARITZA EDITH</t>
+          <t>C001526666 - CANALES AYLLON YESSICA KELLY</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -25750,12 +25750,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>C004014163</t>
+          <t>C001450755</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>C004014163 - PACHAS POLO NOEMI</t>
+          <t>C001450755 - RONCEROS ÑAÑEZ GIOVANA ELIZABETH</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -25791,7 +25791,7 @@
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -25844,12 +25844,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>C001450755</t>
+          <t>C001319626</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>C001450755 - RONCEROS ÑAÑEZ GIOVANA ELIZABETH</t>
+          <t>C001319626 - TUPAC VILCAPUMA MARITZA EDITH</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -25880,12 +25880,12 @@
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -25938,12 +25938,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>C001526666</t>
+          <t>C001646860</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>C001526666 - CANALES AYLLON YESSICA KELLY</t>
+          <t>C001646860 - MARTINEZ VALENCIA JULLIANA DEL CARMEN</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -25974,12 +25974,12 @@
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -26032,12 +26032,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>C001646860</t>
+          <t>C001505052</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>C001646860 - MARTINEZ VALENCIA JULLIANA DEL CARMEN</t>
+          <t>C001505052 - VELASQUEZ ALCA FIORELLA YESICA</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -26068,7 +26068,7 @@
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
@@ -26078,7 +26078,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S275" t="inlineStr"/>
@@ -26220,12 +26220,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>C001505052</t>
+          <t>C001653300</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>C001505052 - VELASQUEZ ALCA FIORELLA YESICA</t>
+          <t>C001653300 - CCAPA CRUZ JUANA</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -26256,17 +26256,17 @@
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S277" t="inlineStr"/>
@@ -26277,12 +26277,12 @@
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -26314,12 +26314,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>C004175861</t>
+          <t>C001506187</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>C004175861 - HERNANDEZ COELLO CARLOS JOHAO</t>
+          <t>C001506187 - CAYCHO FLORES DE GUTIERREZ LUCILA DORA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -26350,12 +26350,12 @@
       <c r="O278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -26408,12 +26408,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>C004187618</t>
+          <t>C001373321</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>C004187618 - QUISPE DE PACHAS ANA MARIA</t>
+          <t>C001373321 - HUAMAN FELIX CARMEN BARBARITA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -26444,12 +26444,12 @@
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -26502,12 +26502,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>C004028239</t>
+          <t>C001379004</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>C004028239 - DE LOS RIOS SALVATIERRA DIANA LIZBETH</t>
+          <t>C001379004 - MUNANTE DE GONZALES CARMELA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -26538,12 +26538,12 @@
       <c r="O280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -26554,17 +26554,13 @@
       <c r="S280" t="inlineStr"/>
       <c r="T280" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr"/>
       <c r="V280" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -26596,12 +26592,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>C001379004</t>
+          <t>C001423708</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>C001379004 - MUNANTE DE GONZALES CARMELA</t>
+          <t>C001423708 - MUNARES LOZA OLGA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -26648,13 +26644,17 @@
       <c r="S281" t="inlineStr"/>
       <c r="T281" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U281" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26686,12 +26686,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>C004178891</t>
+          <t>C001461205</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>C004178891 - MOLINA FUENTES DE MORE ELIZABETH</t>
+          <t>C001461205 - SALCEDO SERVELEON AIDA TEOFILA</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -26722,17 +26722,17 @@
       <c r="O282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S282" t="inlineStr"/>
@@ -26780,12 +26780,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>C001710992</t>
+          <t>C001450465</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>C001710992 - VILLEGAS YALLE LESLIE ANITA</t>
+          <t>C001450465 - AGUILAR YATACO LIDIA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -26816,12 +26816,12 @@
       <c r="O283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -26832,13 +26832,17 @@
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -26870,12 +26874,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>C001731574</t>
+          <t>C001391394</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>C001731574 - GARAY RAMOS GIANCARLO</t>
+          <t>C001391394 - FARFAN CHIRA MARILU GIOVANA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -26916,7 +26920,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S284" t="inlineStr"/>
@@ -26964,12 +26968,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>C001423708</t>
+          <t>C004178891</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>C001423708 - MUNARES LOZA OLGA</t>
+          <t>C004178891 - MOLINA FUENTES DE MORE ELIZABETH</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -27000,12 +27004,12 @@
       <c r="O285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -27058,12 +27062,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>C001461205</t>
+          <t>C004175861</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>C001461205 - SALCEDO SERVELEON AIDA TEOFILA</t>
+          <t>C004175861 - HERNANDEZ COELLO CARLOS JOHAO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -27094,17 +27098,17 @@
       <c r="O286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S286" t="inlineStr"/>
@@ -27152,12 +27156,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>C001476354</t>
+          <t>C004187618</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>C001476354 - SANTIAGO CANCHARI TEODOMIRA ZONIA</t>
+          <t>C004187618 - QUISPE DE PACHAS ANA MARIA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -27183,16 +27187,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q287" t="inlineStr">
@@ -27250,12 +27250,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>C004243882</t>
+          <t>C001476354</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>C004243882 - ELIAS MUNAYCO MARIA GREGORIA</t>
+          <t>C001476354 - SANTIAGO CANCHARI TEODOMIRA ZONIA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -27281,7 +27281,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
@@ -27344,12 +27348,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>C004060593</t>
+          <t>C001731574</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>C004060593 - VALENTIN HUAMAN ROBERTO MARCELINO</t>
+          <t>C001731574 - GARAY RAMOS GIANCARLO</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -27385,7 +27389,7 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -27438,12 +27442,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>C004016311</t>
+          <t>C001710992</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>C004016311 - HUACCAMAYTA ALMEYDA ELIZABETH CELESTE</t>
+          <t>C001710992 - VILLEGAS YALLE LESLIE ANITA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -27484,23 +27488,19 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S290" t="inlineStr"/>
       <c r="T290" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U290" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr"/>
       <c r="V290" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -27532,12 +27532,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>C004042194</t>
+          <t>C004060593</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>C004042194 - MOREYRA TAYPE BEATRIZ</t>
+          <t>C004060593 - VALENTIN HUAMAN ROBERTO MARCELINO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -27568,7 +27568,7 @@
       <c r="O291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q291" t="inlineStr">
@@ -27626,12 +27626,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>C004212960</t>
+          <t>C004180907</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>C004212960 - CHANCA DE LA MATA SABINA</t>
+          <t>C004180907 - VALLE CUETO PIERINA GEORGINA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -27662,7 +27662,7 @@
       <c r="O292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q292" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S292" t="inlineStr"/>
@@ -27720,12 +27720,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>C004180907</t>
+          <t>C004178624</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>C004180907 - VALLE CUETO PIERINA GEORGINA</t>
+          <t>C004178624 - ROJAS OSCO SARITA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -27756,7 +27756,7 @@
       <c r="O293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q293" t="inlineStr">
@@ -27766,7 +27766,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S293" t="inlineStr"/>
@@ -27814,12 +27814,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>C004178624</t>
+          <t>C004212960</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>C004178624 - ROJAS OSCO SARITA</t>
+          <t>C004212960 - CHANCA DE LA MATA SABINA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -27908,12 +27908,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>C001198608</t>
+          <t>C004243882</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>C001198608 - SUAREZ VALLADARES JAQUELIN ROXANA</t>
+          <t>C004243882 - ELIAS MUNAYCO MARIA GREGORIA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -27944,12 +27944,12 @@
       <c r="O295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -28002,12 +28002,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>C001373321</t>
+          <t>C004042194</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>C001373321 - HUAMAN FELIX CARMEN BARBARITA</t>
+          <t>C004042194 - MOREYRA TAYPE BEATRIZ</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -28038,12 +28038,12 @@
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -28096,12 +28096,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>C001391394</t>
+          <t>C004028239</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>C001391394 - FARFAN CHIRA MARILU GIOVANA</t>
+          <t>C004028239 - DE LOS RIOS SALVATIERRA DIANA LIZBETH</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -28142,7 +28142,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S297" t="inlineStr"/>
@@ -28190,12 +28190,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>C001450465</t>
+          <t>C004016311</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>C001450465 - AGUILAR YATACO LIDIA</t>
+          <t>C004016311 - HUACCAMAYTA ALMEYDA ELIZABETH CELESTE</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -28226,17 +28226,17 @@
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S298" t="inlineStr"/>
@@ -28247,12 +28247,12 @@
       </c>
       <c r="U298" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V298" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28284,12 +28284,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>C001506187</t>
+          <t>C001198608</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>C001506187 - CAYCHO FLORES DE GUTIERREZ LUCILA DORA</t>
+          <t>C001198608 - SUAREZ VALLADARES JAQUELIN ROXANA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -28325,7 +28325,7 @@
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
